--- a/samples/wildling/design-data/xlsx/Const.xlsx
+++ b/samples/wildling/design-data/xlsx/Const.xlsx
@@ -18,14 +18,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Const_Growth!$B$10:$E$14]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Idle!$B$2:$E$5]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Const_Party!$B$2:$E$9]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[Const_Codex!$B$11:$E$13]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[Const_Codex!$B$11:$E$14]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[Const_Mission!$B$2:$E$5]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="121">
   <si>
     <t xml:space="preserve">:const BattleConst</t>
   </si>
@@ -352,6 +352,18 @@
   </si>
   <si>
     <t xml:space="preserve">조각 보유 상한</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShardCurrency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조각의 재화 식별자. 이 재화의 비용은 종 단위로 치릅니다</t>
   </si>
   <si>
     <t xml:space="preserve">:const MissionConst</t>
@@ -1214,14 +1226,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.125" customWidth="1"/>
     <col min="2" max="2" width="24.609375" customWidth="1"/>
-    <col min="3" max="3" width="7.03125" customWidth="1"/>
+    <col min="3" max="3" width="9.375" customWidth="1"/>
     <col min="4" max="4" width="8.203125" customWidth="1"/>
-    <col min="5" max="5" width="23.4375" customWidth="1"/>
+    <col min="5" max="5" width="39.84375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1393,8 +1405,22 @@
         <v>108</v>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B11:E13"/>
+  <autoFilter ref="B11:E14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1413,10 +1439,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1441,7 +1467,7 @@
     </row>
     <row r="3">
       <c r="B3" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
@@ -1450,12 +1476,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>8</v>
@@ -1464,12 +1490,12 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
@@ -1478,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/samples/wildling/design-data/xlsx/Const.xlsx
+++ b/samples/wildling/design-data/xlsx/Const.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Battle!$B$9:$E$15]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[Const_Growth!$B$10:$E$14]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Idle!$B$2:$E$5]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Const_Idle!$B$8:$E$10]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Const_Party!$B$2:$E$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[Const_Codex!$B$11:$E$14]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[Const_Mission!$B$2:$E$5]]></definedName>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="128">
   <si>
     <t xml:space="preserve">:const BattleConst</t>
   </si>
@@ -234,6 +234,30 @@
     <t xml:space="preserve">2배 대상. 발견과 조각은 아니다</t>
   </si>
   <si>
+    <t xml:space="preserve">:const NewGameConst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">새 판이 시작할 때 주는 것이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rg_start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">새 판에 지급하는 보상 묶음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpeditionHours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">새 판을 열었을 때 이미 쌓여 있는 탐사 시간</t>
+  </si>
+  <si>
     <t xml:space="preserve">:const PartyConst</t>
   </si>
   <si>
@@ -355,9 +379,6 @@
   </si>
   <si>
     <t xml:space="preserve">ShardCurrency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
   </si>
   <si>
     <t xml:space="preserve">shard</t>
@@ -995,13 +1016,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.09375" customWidth="1"/>
-    <col min="2" max="2" width="19.921875" customWidth="1"/>
+    <col min="1" max="1" width="24.609375" customWidth="1"/>
+    <col min="2" max="2" width="23.4375" customWidth="1"/>
     <col min="3" max="3" width="11.71875" customWidth="1"/>
-    <col min="4" max="5" width="23.4375" customWidth="1"/>
+    <col min="4" max="4" width="23.4375" customWidth="1"/>
+    <col min="5" max="5" width="31.640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1074,8 +1096,65 @@
         <v>68</v>
       </c>
     </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E5"/>
+  <autoFilter ref="B8:E10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1094,10 +1173,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1122,7 +1201,7 @@
     </row>
     <row r="3">
       <c r="B3" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
@@ -1131,12 +1210,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>8</v>
@@ -1145,77 +1224,77 @@
         <v>3</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1238,10 +1317,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1266,7 +1345,7 @@
     </row>
     <row r="3">
       <c r="B3" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
@@ -1275,12 +1354,12 @@
         <v>8</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>8</v>
@@ -1289,12 +1368,12 @@
         <v>12</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
@@ -1303,12 +1382,12 @@
         <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -1317,12 +1396,12 @@
         <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -1331,12 +1410,12 @@
         <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>8</v>
@@ -1345,16 +1424,16 @@
         <v>5000</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1379,7 +1458,7 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>8</v>
@@ -1388,12 +1467,12 @@
         <v>16000</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>8</v>
@@ -1402,21 +1481,21 @@
         <v>9999</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1439,10 +1518,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1467,7 +1546,7 @@
     </row>
     <row r="3">
       <c r="B3" s="5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>8</v>
@@ -1476,12 +1555,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>8</v>
@@ -1490,12 +1569,12 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
@@ -1504,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/samples/wildling/design-data/xlsx/Const.xlsx
+++ b/samples/wildling/design-data/xlsx/Const.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">MaxTurn</t>
   </si>
   <si>
-    <t xml:space="preserve">이 턴에 결착이 없으면 체력 비율로 판정한다</t>
+    <t xml:space="preserve">이 턴에 결착이 없으면 체력 비율로 판정한다. 한 턴은 개체 하나의 행동 한 번이다</t>
   </si>
   <si>
     <t xml:space="preserve">SpeedTiebreak</t>
@@ -615,7 +615,7 @@
     <col min="2" max="2" width="42.1875" customWidth="1"/>
     <col min="3" max="3" width="15.234375" customWidth="1"/>
     <col min="4" max="4" width="25.78125" customWidth="1"/>
-    <col min="5" max="5" width="30.46875" customWidth="1"/>
+    <col min="5" max="5" width="53.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="6">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>76</v>
